--- a/data/trans_orig/IP25A01_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25A01_2023-Edad-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>12230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>15375</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>26748</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>26504</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41938</t>
+          <t>41599</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32311</t>
+          <t>31830</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42774</t>
+          <t>42203</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>30196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41417</t>
+          <t>41564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64851</t>
+          <t>65242</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80221</t>
+          <t>81276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>70,19%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15990</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22672</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17590</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33861</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63742</t>
+          <t>63161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83881</t>
+          <t>83954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77192</t>
+          <t>75934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99648</t>
+          <t>99049</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146165</t>
+          <t>145904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176861</t>
+          <t>176801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>54995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75062</t>
+          <t>74435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62318</t>
+          <t>62271</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85329</t>
+          <t>84022</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>123657</t>
+          <t>123897</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>154581</t>
+          <t>153947</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19964</t>
+          <t>20654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26595</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34569</t>
+          <t>35178</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32911</t>
+          <t>34036</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>34310</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61991</t>
+          <t>62172</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68386</t>
+          <t>68445</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91840</t>
+          <t>91676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89629</t>
+          <t>89708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118144</t>
+          <t>117046</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167444</t>
+          <t>163708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201359</t>
+          <t>201854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50469</t>
+          <t>49448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71871</t>
+          <t>71438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65702</t>
+          <t>66495</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93141</t>
+          <t>93806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>122430</t>
+          <t>124487</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>156937</t>
+          <t>159120</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15899</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33980</t>
+          <t>34514</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21170</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>42697</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41758</t>
+          <t>40643</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69091</t>
+          <t>68445</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81570</t>
+          <t>77724</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136045</t>
+          <t>137115</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>120402</t>
+          <t>120834</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>159871</t>
+          <t>160323</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>220419</t>
+          <t>216512</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>286009</t>
+          <t>286951</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101744</t>
+          <t>101775</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167033</t>
+          <t>174217</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108736</t>
+          <t>107455</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152932</t>
+          <t>152345</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>221874</t>
+          <t>221348</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300070</t>
+          <t>301145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,22%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39600</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27604</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31357</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57021</t>
+          <t>55948</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>46803</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77160</t>
+          <t>76225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59949</t>
+          <t>59199</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90821</t>
+          <t>89540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>114060</t>
+          <t>112334</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158085</t>
+          <t>153959</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>243867</t>
+          <t>246619</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>309369</t>
+          <t>311198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>322697</t>
+          <t>325464</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>378834</t>
+          <t>381180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588757</t>
+          <t>588608</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>677391</t>
+          <t>675183</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>259330</t>
+          <t>258461</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>339537</t>
+          <t>338714</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>290080</t>
+          <t>288335</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>347904</t>
+          <t>345296</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>563647</t>
+          <t>567161</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>664596</t>
+          <t>661852</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A01_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25A01_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1146</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3920</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4306</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3990</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1146</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4281</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5392</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4384</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8294</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>11044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17292</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12933</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21856</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>35,21%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>26,33%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>44,5%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13196</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8380</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18821</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>33,57%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20605</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26748</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>29803</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26504</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41599</t>
+          <t>36885</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29154</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24419</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>33878</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>59,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>49,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>68,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>37340</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31830</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>42203</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>66,6%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>56,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35748</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30196</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41564</t>
+          <t>37799</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>73088</t>
+          <t>62370</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65242</t>
+          <t>54776</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81276</t>
+          <t>68544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>68,57%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49115</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49115</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>49115</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>56066</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>56066</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56066</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>115794</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115794</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115794</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1844</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9541</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8702</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4605</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>14085</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4429</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>13008</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>5,56%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5317</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2298</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>11167</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9149</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>19286</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14038</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8962</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21143</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9364</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4940</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15142</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23773</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>32379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74345</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>64471</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>84220</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>53,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>73774</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63161</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>83954</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>47,12%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>53,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87873</t>
+          <t>66443</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75934</t>
+          <t>57821</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99049</t>
+          <t>76287</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>161646</t>
+          <t>140789</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145904</t>
+          <t>128250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176801</t>
+          <t>154696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>64581</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56382</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>74802</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>41,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>35,79%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>47,49%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>64710</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>54995</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>74435</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>41,34%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>35,13%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>47,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73784</t>
+          <t>59209</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62271</t>
+          <t>50333</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84022</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>138494</t>
+          <t>123790</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>123897</t>
+          <t>109852</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>153947</t>
+          <t>136152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>156550</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>156550</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>156550</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>142968</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>142968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>142968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>339104</t>
+          <t>300490</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>339104</t>
+          <t>300490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>339104</t>
+          <t>300490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5577</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1942</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11184</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>8290</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3465</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20654</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13893</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22519</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14977</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31304</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>15,64%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>22722</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>15190</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>35178</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>20,41%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>20664</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34036</t>
+          <t>29059</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>46800</t>
+          <t>43183</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>34310</t>
+          <t>32632</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>62172</t>
+          <t>55362</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>98729</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>86724</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>111934</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>49,33%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>80568</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>68445</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>91676</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>46,75%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>103214</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89708</t>
+          <t>72142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117046</t>
+          <t>95159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>183782</t>
+          <t>182604</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>163708</t>
+          <t>164865</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201854</t>
+          <t>198258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>73301</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>61525</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>85619</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>60744</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>49448</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>71438</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>35,25%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>79596</t>
+          <t>63364</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66495</t>
+          <t>52533</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93806</t>
+          <t>75224</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>140339</t>
+          <t>136666</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124487</t>
+          <t>121294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159120</t>
+          <t>153608</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>172324</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>172324</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>172324</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173849</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>384814</t>
+          <t>373975</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384814</t>
+          <t>373975</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>384814</t>
+          <t>373975</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6562</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3064</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13221</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>6121</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2912</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>11535</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20525</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>29102</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20736</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>40636</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>13,89%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>24283</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>15899</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>34514</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>23545</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42697</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>54294</t>
+          <t>52647</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40643</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68445</t>
+          <t>66394</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>139509</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>121221</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>157850</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>47,67%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>41,42%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>53,94%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>116586</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>77724</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>137115</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>42,99%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>28,66%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>50,57%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>140975</t>
+          <t>116542</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>120834</t>
+          <t>102906</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>160323</t>
+          <t>130250</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>257561</t>
+          <t>256051</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>216512</t>
+          <t>231059</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>286951</t>
+          <t>279414</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>51,28%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>117473</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>99114</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>138730</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>40,14%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>47,41%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>124174</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>101775</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>174217</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>45,79%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>37,53%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>64,25%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>127901</t>
+          <t>105788</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107455</t>
+          <t>92017</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152345</t>
+          <t>119787</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>252075</t>
+          <t>223260</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>221348</t>
+          <t>200588</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>301145</t>
+          <t>249977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>271164</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>271164</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>271164</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>252203</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>252203</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>252203</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>576647</t>
+          <t>544847</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>576647</t>
+          <t>544847</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>576647</t>
+          <t>544847</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>16697</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>10396</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>25550</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>24259</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>16804</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>35969</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26781</t>
+          <t>29533</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>41773</t>
+          <t>38054</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>28143</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55948</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>68328</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>55354</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>83056</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>60753</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>46803</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>76225</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>11,62%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>73045</t>
+          <t>57564</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59199</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89540</t>
+          <t>72067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>133798</t>
+          <t>125892</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112334</t>
+          <t>110261</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>153959</t>
+          <t>145889</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>329874</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>302197</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>353176</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>47,16%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>43,21%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>50,5%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>406</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>284123</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>246619</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>311198</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>43,3%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>37,59%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>47,43%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>352667</t>
+          <t>279373</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>325464</t>
+          <t>257937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>381180</t>
+          <t>300503</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>636791</t>
+          <t>609247</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588608</t>
+          <t>578410</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>675183</t>
+          <t>642191</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>286968</t>
+          <t>284509</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>258461</t>
+          <t>258578</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>338714</t>
+          <t>312152</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>317028</t>
+          <t>261577</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>288335</t>
+          <t>242563</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>345296</t>
+          <t>282224</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>603997</t>
+          <t>546085</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>567161</t>
+          <t>514903</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>661852</t>
+          <t>578598</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>656104</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>656104</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>656104</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619872</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619872</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619872</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1416359</t>
+          <t>1319278</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1416359</t>
+          <t>1319278</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1416359</t>
+          <t>1319278</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
